--- a/output/alunos_em_curso.xlsx
+++ b/output/alunos_em_curso.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="296">
   <si>
     <t>number</t>
   </si>
@@ -107,9 +107,6 @@
     <t>MIGUEL CORACY GOULART MARTINS</t>
   </si>
   <si>
-    <t>RAFAEL DEPIANTTI MERLO</t>
-  </si>
-  <si>
     <t>RAFAELA LUIZA DEPIANTTI DUTRA GONCALVES</t>
   </si>
   <si>
@@ -218,9 +215,6 @@
     <t>VITORIA MORAES SPAGNOL</t>
   </si>
   <si>
-    <t>YAN PIETRO SANTOS DE MACEDO</t>
-  </si>
-  <si>
     <t>YASMIN MARCELLY SILVA OLIVEIRA</t>
   </si>
   <si>
@@ -275,9 +269,6 @@
     <t>KEMILLY EDELYN MIRANDA BARBOSA</t>
   </si>
   <si>
-    <t>LUIZ GABRIEL DE SOUZA BORGES</t>
-  </si>
-  <si>
     <t>LYNSKELME SANTOS LIMEIRA SOUZA</t>
   </si>
   <si>
@@ -302,9 +293,6 @@
     <t>RICARDO ALOQUIO NOGUEIRA</t>
   </si>
   <si>
-    <t>RYAN MOURA FAUSTINO</t>
-  </si>
-  <si>
     <t>TATIANA MENDES NOGUEIRA PORPHIRIO</t>
   </si>
   <si>
@@ -317,145 +305,151 @@
     <t>YASMIN ALVES DE OLIVEIRA</t>
   </si>
   <si>
+    <t>ISAK ALVARENGA CHRIST</t>
+  </si>
+  <si>
+    <t>LEONARDO DE SOUZA DE BORTOLI</t>
+  </si>
+  <si>
+    <t>ALICE VITORIA FALCAO DE JESUS</t>
+  </si>
+  <si>
+    <t>ALICIA DOS SANTOS ROCHA</t>
+  </si>
+  <si>
+    <t>ARTHUR GOMES SPAGNOL</t>
+  </si>
+  <si>
+    <t>AUGUSTO DOS SANTOS GERONIMO</t>
+  </si>
+  <si>
+    <t>CAMILLY VICTORIA GUIMARAES DA SILVA LOURENCO</t>
+  </si>
+  <si>
+    <t>CAUA FERREIRA DE JESUS</t>
+  </si>
+  <si>
+    <t>CELSO ARTHUR RANGEL PAIXAO PEREIRA</t>
+  </si>
+  <si>
+    <t>DAVI DE AMORIM PIRES</t>
+  </si>
+  <si>
+    <t>GABRIELLE ANDRADE DA CRUZ</t>
+  </si>
+  <si>
+    <t>JANAINA MARTINS BIRCHENER</t>
+  </si>
+  <si>
+    <t>JOAO VICTOR LIMA BRASIL</t>
+  </si>
+  <si>
+    <t>JOAO VICTOR MARQUES DE FREITAS DIAS</t>
+  </si>
+  <si>
+    <t>JOAO VITOR GLEYCIANO DE SOUZA FREITAS</t>
+  </si>
+  <si>
+    <t>KAUA NORBIM PEREIRA</t>
+  </si>
+  <si>
+    <t>LUANA GUIMARAES SANTOS</t>
+  </si>
+  <si>
+    <t>LUCAS DA SILVA SANTOS</t>
+  </si>
+  <si>
+    <t>MAISA SOUSA PEREIRA</t>
+  </si>
+  <si>
+    <t>MARIA EDUARDA ALVES BORGES</t>
+  </si>
+  <si>
+    <t>MERIELLY MATTOS LIMA</t>
+  </si>
+  <si>
+    <t>MYGUEL AUGUSTO DA SILVA DE OLIVEIRA PEREIRA</t>
+  </si>
+  <si>
+    <t>NICOLLY ALMEIDA REIS</t>
+  </si>
+  <si>
+    <t>NICOLY ADIELES PAULINO DOS ANJOS</t>
+  </si>
+  <si>
+    <t>SALOMAO GOMES SOUZA</t>
+  </si>
+  <si>
+    <t>ANA CLARA DA SILVA ALVES</t>
+  </si>
+  <si>
+    <t>ANA CLARA PEREIRA BATISTA</t>
+  </si>
+  <si>
+    <t>ANDERSON DOS SANTOS RODRIGUES</t>
+  </si>
+  <si>
+    <t>ERICK PINTO NETTO</t>
+  </si>
+  <si>
+    <t>GABRIEL ZAMBOM DE ASSIS</t>
+  </si>
+  <si>
+    <t>GUSTAVO GABRIEL BARDES DA SILVA</t>
+  </si>
+  <si>
+    <t>HUGO MIGUEL DA VITORIA DA SILVA</t>
+  </si>
+  <si>
+    <t>JOAO VITOR SABINO ESQUIVEL</t>
+  </si>
+  <si>
+    <t>LUARA GABRIELY SANTOS DEMETRIO</t>
+  </si>
+  <si>
+    <t>LUIZ HENRIQUE MOURA</t>
+  </si>
+  <si>
+    <t>MARIA EDUARDA AZEVEDO MEDEIROS</t>
+  </si>
+  <si>
+    <t>MARIA JULIA SANTANA REIS</t>
+  </si>
+  <si>
+    <t>MIKAELLA DA CONCEICAO SILVEIRA DO NASCIMENTO COSTA</t>
+  </si>
+  <si>
+    <t>RAI DA SILVA DOS REMEDIOS</t>
+  </si>
+  <si>
+    <t>RODRIGO ISAC FELIX MADEIRA</t>
+  </si>
+  <si>
+    <t>SHARLLA GABRIELY BATISTA DA SILVA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>SOPHIE DAYENDER DOS PASSOS DA COSTA</t>
+  </si>
+  <si>
+    <t>THAYSSA NUNES DA VITORIA DA CRUZ</t>
+  </si>
+  <si>
+    <t>YASMYM VICTORIA DE AGUIAR DOS SANTOS</t>
+  </si>
+  <si>
+    <t>PATRICIA DO NASCIMENTO ALMEIDA</t>
+  </si>
+  <si>
+    <t>KAYKY SANTOS DA SILVA</t>
+  </si>
+  <si>
+    <t>EMANUELLY BENEDICTO SANTIAGO</t>
+  </si>
+  <si>
     <t>YURI VIEIRA RODRIGUES</t>
   </si>
   <si>
-    <t>ISAK ALVARENGA CHRIST</t>
-  </si>
-  <si>
-    <t>LEONARDO DE SOUZA DE BORTOLI</t>
-  </si>
-  <si>
-    <t>ALICE VITORIA FALCAO DE JESUS</t>
-  </si>
-  <si>
-    <t>ALICIA DOS SANTOS ROCHA</t>
-  </si>
-  <si>
-    <t>ARTHUR GOMES SPAGNOL</t>
-  </si>
-  <si>
-    <t>AUGUSTO DOS SANTOS GERONIMO</t>
-  </si>
-  <si>
-    <t>CAMILLY VICTORIA GUIMARAES DA SILVA LOURENCO</t>
-  </si>
-  <si>
-    <t>CAUA FERREIRA DE JESUS</t>
-  </si>
-  <si>
-    <t>CELSO ARTHUR RANGEL PAIXAO PEREIRA</t>
-  </si>
-  <si>
-    <t>DAVI DE AMORIM PIRES</t>
-  </si>
-  <si>
-    <t>GABRIELLE ANDRADE DA CRUZ</t>
-  </si>
-  <si>
-    <t>JANAINA MARTINS BIRCHENER</t>
-  </si>
-  <si>
-    <t>JOAO VICTOR LIMA BRASIL</t>
-  </si>
-  <si>
-    <t>JOAO VICTOR MARQUES DE FREITAS DIAS</t>
-  </si>
-  <si>
-    <t>JOAO VITOR GLEYCIANO DE SOUZA FREITAS</t>
-  </si>
-  <si>
-    <t>KAUA NORBIM PEREIRA</t>
-  </si>
-  <si>
-    <t>LUANA GUIMARAES SANTOS</t>
-  </si>
-  <si>
-    <t>LUCAS DA SILVA SANTOS</t>
-  </si>
-  <si>
-    <t>MAISA SOUSA PEREIRA</t>
-  </si>
-  <si>
-    <t>MARIA EDUARDA ALVES BORGES</t>
-  </si>
-  <si>
-    <t>MERIELLY MATTOS LIMA</t>
-  </si>
-  <si>
-    <t>MYGUEL AUGUSTO DA SILVA DE OLIVEIRA PEREIRA</t>
-  </si>
-  <si>
-    <t>NICOLLY ALMEIDA REIS</t>
-  </si>
-  <si>
-    <t>NICOLY ADIELES PAULINO DOS ANJOS</t>
-  </si>
-  <si>
-    <t>SALOMAO GOMES SOUZA</t>
-  </si>
-  <si>
-    <t>PATRICIA DO NASCIMENTO ALMEIDA</t>
-  </si>
-  <si>
-    <t>ANA CLARA DA SILVA ALVES</t>
-  </si>
-  <si>
-    <t>ANA CLARA PEREIRA BATISTA</t>
-  </si>
-  <si>
-    <t>ANDERSON DOS SANTOS RODRIGUES</t>
-  </si>
-  <si>
-    <t>EMANUELLY BENEDICTO SANTIAGO</t>
-  </si>
-  <si>
-    <t>ERICK PINTO NETTO</t>
-  </si>
-  <si>
-    <t>GABRIEL ZAMBOM DE ASSIS</t>
-  </si>
-  <si>
-    <t>GUSTAVO GABRIEL BARDES DA SILVA</t>
-  </si>
-  <si>
-    <t>HUGO MIGUEL DA VITORIA DA SILVA</t>
-  </si>
-  <si>
-    <t>JOAO VITOR SABINO ESQUIVEL</t>
-  </si>
-  <si>
-    <t>LUARA GABRIELY SANTOS DEMETRIO</t>
-  </si>
-  <si>
-    <t>LUIZ HENRIQUE MOURA</t>
-  </si>
-  <si>
-    <t>MARIA EDUARDA AZEVEDO MEDEIROS</t>
-  </si>
-  <si>
-    <t>MARIA JULIA SANTANA REIS</t>
-  </si>
-  <si>
-    <t>MIKAELLA DA CONCEICAO SILVEIRA DO NASCIMENTO COSTA</t>
-  </si>
-  <si>
-    <t>RAI DA SILVA DOS REMEDIOS</t>
-  </si>
-  <si>
-    <t>RODRIGO ISAC FELIX MADEIRA</t>
-  </si>
-  <si>
-    <t>SHARLLA GABRIELY BATISTA DA SILVA DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>SOPHIE DAYENDER DOS PASSOS DA COSTA</t>
-  </si>
-  <si>
-    <t>THAYSSA NUNES DA VITORIA DA CRUZ</t>
-  </si>
-  <si>
-    <t>YASMYM VICTORIA DE AGUIAR DOS SANTOS</t>
+    <t>STEFANY DE AZEVEDO XAVIER</t>
   </si>
   <si>
     <t>ANA LUIZA DE CASTRO SILVA</t>
@@ -473,9 +467,6 @@
     <t>DANIEL BARBOSA DE ARAUJO</t>
   </si>
   <si>
-    <t>DANIEL GUIMARAES SANTOS</t>
-  </si>
-  <si>
     <t>DIOGO TRASPADINI SANTOS</t>
   </si>
   <si>
@@ -515,6 +506,15 @@
     <t>YURI SOARES DE AMURIM</t>
   </si>
   <si>
+    <t>VICTORIA GUIMARAES FERREIRA</t>
+  </si>
+  <si>
+    <t>GUILHERME DOS SANTOS ALVES DA CONCEICAO</t>
+  </si>
+  <si>
+    <t>DAVI DOS SANTOS AMBROSIO</t>
+  </si>
+  <si>
     <t>ANA BEATRIZ APOLINARIO ZANON</t>
   </si>
   <si>
@@ -560,9 +560,6 @@
     <t>LUCAS GABRIEL SILVA LEMOS</t>
   </si>
   <si>
-    <t>MARIA EDUARDA MARTINS ROSA</t>
-  </si>
-  <si>
     <t>MARIA TEREZA LIMA LASCOSCK</t>
   </si>
   <si>
@@ -584,9 +581,6 @@
     <t>PEDRO EMANUEL MARCELINO COSTA</t>
   </si>
   <si>
-    <t>RYANA SIQUEIRA DE OLIVEIRA</t>
-  </si>
-  <si>
     <t>SULAMITA VITORIA SOUZA MENEZES</t>
   </si>
   <si>
@@ -596,6 +590,18 @@
     <t>VINICIUS SILVARES MARINHEIRO DOS SANTOS</t>
   </si>
   <si>
+    <t>CAMILLA DE JESUS SANTOS</t>
+  </si>
+  <si>
+    <t>LETICIA STRELOVO SOUSA</t>
+  </si>
+  <si>
+    <t>DAVI MOULIN ZANON</t>
+  </si>
+  <si>
+    <t>KASSIANE ROCHA SIQUEIRA</t>
+  </si>
+  <si>
     <t>ANDRESSA VITORIA DE SOUZA</t>
   </si>
   <si>
@@ -614,21 +620,12 @@
     <t>DAVI EDUARDO SOARES ANTUNES</t>
   </si>
   <si>
-    <t>DAVI MOULIN ZANON</t>
-  </si>
-  <si>
     <t>EMANUEL GUIMARAES MARIANO</t>
   </si>
   <si>
-    <t>ERIK DA SILVA MORAIS</t>
-  </si>
-  <si>
     <t>GEFERSSON SOUZA LIMA</t>
   </si>
   <si>
-    <t>GUILHERME DOS SANTOS ALVES DA CONCEICAO</t>
-  </si>
-  <si>
     <t>IUDI RODRIGUES DE OLIVEIRA</t>
   </si>
   <si>
@@ -656,6 +653,9 @@
     <t>AYELLE SANTOS DE JESUS</t>
   </si>
   <si>
+    <t>JULIARA DE MOURA LOPES</t>
+  </si>
+  <si>
     <t>ADRIEL BRANDES DOS SANTOS</t>
   </si>
   <si>
@@ -906,6 +906,12 @@
   </si>
   <si>
     <t>YASMYN ALVES FERREIRA</t>
+  </si>
+  <si>
+    <t>GUILHERME DE MATOS CAMILO</t>
+  </si>
+  <si>
+    <t>KAUA SILVA MONTEIRO</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -1480,7 +1486,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
         <v>27</v>
@@ -1488,7 +1494,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
         <v>28</v>
@@ -1496,7 +1502,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
         <v>29</v>
@@ -1504,7 +1510,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
         <v>30</v>
@@ -1512,7 +1518,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
@@ -1520,7 +1526,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
         <v>32</v>
@@ -1528,18 +1534,10 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>35</v>
-      </c>
-      <c r="B34" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1835,7 +1833,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -2050,6 +2048,22 @@
         <v>293</v>
       </c>
     </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>295</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2057,7 +2071,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -2077,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2085,7 +2099,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2093,7 +2107,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2101,7 +2115,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2109,7 +2123,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2117,7 +2131,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2125,7 +2139,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2133,7 +2147,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2141,7 +2155,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2149,7 +2163,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2157,7 +2171,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2165,7 +2179,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2173,7 +2187,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2181,7 +2195,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2189,7 +2203,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2197,7 +2211,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2205,7 +2219,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2213,7 +2227,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2221,7 +2235,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2229,7 +2243,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2237,7 +2251,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2245,7 +2259,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2253,7 +2267,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2261,7 +2275,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2269,7 +2283,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2277,7 +2291,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2285,7 +2299,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2293,7 +2307,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2301,31 +2315,23 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2335,7 +2341,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -2355,7 +2361,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2363,7 +2369,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2371,7 +2377,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2379,7 +2385,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2387,7 +2393,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2395,7 +2401,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2403,7 +2409,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2411,7 +2417,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2419,7 +2425,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2427,7 +2433,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2435,7 +2441,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2443,7 +2449,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2451,7 +2457,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2459,7 +2465,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2467,7 +2473,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2475,143 +2481,119 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32">
-        <v>34</v>
-      </c>
-      <c r="B32" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>36</v>
-      </c>
-      <c r="B33" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>37</v>
-      </c>
-      <c r="B34" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2621,7 +2603,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -2641,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2649,7 +2631,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2657,7 +2639,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2665,7 +2647,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2673,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2681,7 +2663,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2689,7 +2671,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2697,7 +2679,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2705,7 +2687,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2713,7 +2695,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2721,7 +2703,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2729,7 +2711,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2737,7 +2719,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2745,7 +2727,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2753,7 +2735,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2761,7 +2743,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2769,7 +2751,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2777,7 +2759,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2785,7 +2767,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2793,7 +2775,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2801,7 +2783,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2809,7 +2791,7 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2817,15 +2799,7 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -2835,7 +2809,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -2855,7 +2829,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2863,7 +2837,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2871,143 +2845,175 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>143</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>27</v>
+      </c>
+      <c r="B23" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -3017,7 +3023,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -3037,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3045,7 +3051,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3053,7 +3059,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3061,7 +3067,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3069,118 +3075,134 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3191,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -3328,7 +3350,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
         <v>178</v>
@@ -3336,7 +3358,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
         <v>179</v>
@@ -3344,7 +3366,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
         <v>180</v>
@@ -3352,7 +3374,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
         <v>181</v>
@@ -3360,7 +3382,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
         <v>182</v>
@@ -3368,7 +3390,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
         <v>183</v>
@@ -3376,7 +3398,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
         <v>184</v>
@@ -3384,7 +3406,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
         <v>185</v>
@@ -3392,7 +3414,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
         <v>186</v>
@@ -3400,7 +3422,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
         <v>187</v>
@@ -3408,7 +3430,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
         <v>188</v>
@@ -3416,10 +3438,26 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -3429,11 +3467,11 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3449,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3457,7 +3495,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3465,7 +3503,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3473,7 +3511,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3481,7 +3519,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3489,118 +3527,102 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
         <v>209</v>
       </c>
     </row>
